--- a/Table_S7.xlsx
+++ b/Table_S7.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_TE_background" sheetId="1" r:id="Rf8fd74da6ece45ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_TE_background" sheetId="1" r:id="R613d063e0e7540ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -336,7 +336,7 @@
   <x:sheetData>
     <x:row r="1" s="13" customFormat="1" ht="36" customHeight="1">
       <x:c r="A1" s="22" t="str">
-        <x:v>Table S7. Strict TE-only background comparison and initial threshold robustness for HSF-family motif density.</x:v>
+        <x:v>Table S7. Strict TE-only background comparison of HSF-family motif density at relative PWM-score thresholds of 0.85 and 0.90.</x:v>
       </x:c>
       <x:c r="B1" s="1" t="n"/>
       <x:c r="C1" s="1" t="n"/>
